--- a/genai_bug_cases.xlsx
+++ b/genai_bug_cases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GenAI Bug Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bug Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,26 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +52,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,433 +440,553 @@
   </sheetPr>
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Case ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Student Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>LLM Model</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Original Code</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>New Code (Bug)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Initial Reflection</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>GenAI Label</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>GenAI Guidance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>New Reflection</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Case 1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Student Name
+(First Last)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LLM Model
+Name Used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Original Code Snippet</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>New Code Snippet
+with Bugs</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Your Initial
+Self-Reflection</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GenAI's Label
+("Good" or "Bad")</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>GenAI's Guidance</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Your New
+Self-Reflection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="120" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Devin Myers</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>criterion = nn.CrossEntropyLoss()</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>criterion = nn.MSELoss()</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>I think the error happens because MSELoss expects the output and target to have the same shape, but our model outputs a tensor of shape [batch, 10] while labels are just integers of shape [batch]. CrossEntropyLoss handles integer class labels internally, but MSELoss does not.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>You've identified the shape mismatch, which is a good start. But consider: even if you one-hot encoded the labels to fix the shape, would MSELoss still be appropriate for a classification task? Think about what mathematical property of the loss function makes CrossEntropyLoss better suited for classification compared to MSELoss. What does CrossEntropyLoss compute internally that MSELoss does not?</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>MSELoss is designed for regression — it penalizes the squared difference between predicted and target values. Even with one-hot labels, MSE treats all output neurons independently and doesn't account for the fact that exactly one class should be chosen. CrossEntropyLoss applies log-softmax internally, which converts raw logits into a probability distribution, then computes the negative log-likelihood of the correct class. This makes gradients much sharper for the correct class, driving the model to assign high probability to one class. The core issue is using a regression loss for a classification problem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Devin Myers</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>LEARNING_RATE = 0.001</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>LEARNING_RATE = 10.0</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>The learning rate is too big so the model can't learn properly.</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>You've noted the learning rate is 'too big,' but that's quite surface-level. Can you explain *why* a large learning rate prevents learning? Think about what happens to the gradient update step when the learning rate is very large. What specific numerical phenomenon occurs in the loss values? And why does the accuracy hover around 10% specifically — what does that number correspond to in a 10-class problem?</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>When the learning rate is 10.0, each gradient descent step overshoots the loss minimum by a huge margin. The weight updates are so large that instead of descending toward a good solution, the parameters oscillate wildly or diverge entirely. This causes the loss to become NaN (not a number) because the logits grow so large that floating-point overflow occurs. With NaN outputs, the model's predictions are essentially random — and with 10 classes, random guessing gives exactly 10% accuracy. The fix is to use a small learning rate like 0.001 so gradient steps are small enough to converge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Vina Dang</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GPT</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>x = np.array(data)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>x = data</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>I think the issue is that the data format changed and the model might not accept it anymore.</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>NUM_CLASSES = 10</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NUM_CLASSES = 5</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>The model only has 5 output neurons but Fashion-MNIST has 10 classes (labels 0-9). When a label like 7 appears, it's out of bounds for the 5-neuron output layer.</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>What type does the model expect for input? Are all operations valid on this new type?</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>The issue is that the model expects a NumPy array, but I changed it to a list, which breaks later computations.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Case 2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>model.fit(X_train, y_train)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>model.fit(X_test, y_test)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>The model might not be learning properly.</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>You correctly identified the mismatch between output size and label range. But think more precisely: *where* does the out-of-bounds error actually occur? Is it in the model's forward pass, or in the loss computation? What specific operation inside CrossEntropyLoss requires the output dimension to match the number of possible label values? Understanding this will help you debug similar dimension mismatches in the future.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>The error occurs inside CrossEntropyLoss, not in the model itself. The model's forward pass works fine — it produces a tensor of shape [batch, 5]. But CrossEntropyLoss internally applies log_softmax over the output dimension and then indexes into position `label` to get the loss for each sample. When a label is 7 but the output tensor only has indices 0-4, this indexing operation raises an IndexError. The model architecture and loss function must agree on the number of classes. The fix is to set NUM_CLASSES = 10 to match the dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Vina Dang</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>transforms.Compose([
+    transforms.ToTensor(),
+    transforms.Normalize((0.5,), (0.5,))
+])</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>transforms.Compose([
+    transforms.ToTensor(),
+    # Normalize removed
+])</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Without normalization the pixel values are between 0 and 1 instead of -1 and 1. The model should still work but might be slightly worse.</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>What is the purpose of training vs testing data?</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>I accidentally trained on test data, which ruins evaluation and causes misleading performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Case 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>learning_rate = 0.01</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>learning_rate = 10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>The model is not converging.</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>The learning rate is too high, causing unstable updates and preventing convergence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Case 4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>epochs = 10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>epochs = 1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>The model accuracy is low.</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>You're right that the model still runs, and you correctly noted the value range changes. But your reflection is vague — 'slightly worse' doesn't demonstrate deep understanding. Think about *why* normalization helps neural networks train. Consider: what happens to the initial weight distributions and gradient magnitudes when inputs have a non-zero mean? How does this specifically affect the speed of convergence during backpropagation?</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Normalization centers the data around 0 with unit-like variance. Without it, input pixels are all positive (0 to 1) with mean ~0.5. This means the first layer always receives positive inputs, which biases the gradient updates — all weights in the first layer get gradients of the same sign, causing a zig-zag optimization path that slows convergence. With centered data (mean 0), gradients can be both positive and negative, allowing more direct paths to the optimum. The model still learns because the optimizer eventually compensates, but it takes more epochs to reach the same accuracy. Normalization is especially important for deeper networks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Devin Myers</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>train_dataset = datasets.FashionMNIST(
+    root='./data', train=True,
+    download=True, transform=transform
+)</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>train_dataset = datasets.FashionMNIST(...)
+train_dataset.targets = train_dataset.targets[
+    torch.randperm(len(train_dataset.targets))
+]</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>I shuffled the labels randomly so now images don't match their correct classes. The model is trying to learn incorrect mappings, so it can't learn any real patterns.</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Did the model train long enough to learn patterns?</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>The model didn’t train enough, so it underfits the data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Case 5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>y = data['label']</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>y = data['labels']</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>There may be a typo.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>The column name is incorrect, causing a key error.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Case 6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>from sklearn.model_selection import train_test_split</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>from sklearn.model_selection import train_test_splt</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Import error might be happening.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>There is a typo in the import function name.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Case 7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>model.predict(X_test)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>model.predict(X_train)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Predictions seem too accurate.</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>You've correctly identified that the labels are mismatched. But think deeper: if the model is trying to learn 'incorrect' mappings, is it truly unable to learn *any* patterns? Could a powerful enough model memorize random label assignments on the training set? If so, what would you expect to see in terms of training accuracy vs test accuracy? What does this tell you about the difference between memorization and generalization?</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>With shuffled labels, the mapping from images to labels is random — there's no consistent visual pattern the model can extract. A very large model might memorize the training set (getting high training accuracy) but this would be pure overfitting, and test accuracy would remain at ~10% since the test labels are still correct. In our case, the CNN is too small to memorize 60,000 random mappings, so both training and test accuracy stay near 10%. This demonstrates the fundamental difference between learning meaningful features (generalization) vs. memorizing noise. It also shows why data quality is as important as model architecture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Vina Dang</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>nn.Conv2d(1, 32, ...), nn.ReLU(), nn.MaxPool2d(2),
+nn.Conv2d(32, 64, ...), nn.ReLU(), nn.MaxPool2d(2),
+...
+nn.Linear(64*7*7, 128), nn.ReLU(), ...</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>nn.Conv2d(1, 32, ...), nn.MaxPool2d(2),
+nn.Conv2d(32, 64, ...), nn.MaxPool2d(2),
+...
+nn.Linear(64*7*7, 128), ...
+# All ReLU activations removed</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Without ReLU the network is just doing linear math so it can't learn complex patterns. It should still work but accuracy will be lower.</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Are you evaluating on unseen data?</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>I used training data instead of test data, causing overestimated accuracy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Case 8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>X = X / 255.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>X = X</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Model performance dropped.</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>You have the right intuition that removing nonlinearities makes the network 'linear.' But can you be more precise? What mathematical property makes stacking multiple linear layers equivalent to a single linear layer? And given that the network becomes linear, what kind of decision boundaries can it learn? Compare this to what Fashion-MNIST actually requires — are clothing items separable by straight lines in pixel space?</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Without activation functions, each layer computes output = W*x + b. Composing multiple such layers gives output = W3*(W2*(W1*x + b1) + b2) + b3 = W_combined*x + b_combined — it's equivalent to a single linear transformation regardless of depth. This means the deep CNN collapses to a linear classifier. Linear classifiers can only draw hyperplane decision boundaries in the feature space. Fashion-MNIST has 10 classes with complex visual features (texture, shape, edges), so straight-line boundaries in pixel space are insufficient. The model can still separate some easy classes (like Trousers vs Bags) but fails on similar ones (Shirt vs Pullover). ReLU introduces nonlinearity, allowing the network to learn curved, complex decision boundaries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Devin Myers</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>nn.Conv2d(1, 32, kernel_size=3, padding=1)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>nn.Conv2d(3, 32, kernel_size=3, padding=1)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>I changed the input channels from 1 to 3. Fashion-MNIST is grayscale so it only has 1 channel, but the model now expects 3 channels like RGB images.</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>What role does normalization play?</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Removing normalization caused poor model performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Case 9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>batch_size = 32</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>batch_size = 10000</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Training crashes.</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Batch size is too large, causing memory issues.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Case 10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>loss='categorical_crossentropy'</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>loss='mean_squared_error'</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Accuracy is worse.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>You've correctly identified the channel mismatch. But think about this from a lower level: what is a 'channel' in the context of a convolution operation? How does the Conv2d kernel's shape relate to the input tensor's shape? When PyTorch reports the error about 'expected 3 channels but got 1,' what specific tensor dimension is it comparing? Understanding tensor shapes through the network will help you debug more complex architecture issues.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>A Conv2d layer with in_channels=3 creates kernels of shape [out_channels, 3, H, W]. During convolution, PyTorch multiplies each kernel across all input channels simultaneously — so the kernel's second dimension must exactly match the input tensor's channel dimension. Fashion-MNIST images are [batch, 1, 28, 28] (1 channel), but our kernel expects [batch, 3, 28, 28]. PyTorch checks this at runtime and raises a RuntimeError because it can't perform the element-wise multiplication across mismatched dimensions. The fix is to set in_channels=1 to match grayscale input, or convert images to 3 channels by repeating the grayscale channel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Vina Dang</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>optimizer.zero_grad()
+outputs = model(images)
+loss = criterion(outputs, labels)
+loss.backward()
+optimizer.step()</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t># optimizer.zero_grad() REMOVED
+outputs = model(images)
+loss = criterion(outputs, labels)
+loss.backward()
+optimizer.step()</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Without zero_grad the gradients keep adding up from previous batches, so the weight updates become wrong and training is messed up.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Bad</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Is this loss function appropriate for classification?</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MSE is not suitable for classification tasks, leading to poor results.</t>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>You've identified gradient accumulation, which is correct. But think more carefully: in PyTorch, gradients are accumulated by *addition*. If each batch contributes a gradient g_i, after N batches without zeroing, the accumulated gradient is g_1 + g_2 + ... + g_N. How does this compare to what the optimizer 'thinks' it's working with? Is there any scenario where gradient accumulation is intentionally used? What does this tell you about *why* the training is 'messed up' — is the direction wrong, or the magnitude?</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Without zero_grad(), each call to loss.backward() adds the new gradients to whatever is already stored in .grad. After N batches, the gradient is the sum of N individual batch gradients. The optimizer (Adam) then applies a step using this accumulated sum as if it were a single batch gradient. The direction might be approximately correct (it's a sum of valid gradients), but the magnitude is N times larger than expected. This is effectively like multiplying the learning rate by N, which grows every batch within an epoch. By the end of one epoch (~937 batches), the effective LR is 937x too large, causing the same divergence as an extremely high learning rate. Interestingly, gradient accumulation is sometimes used intentionally to simulate larger batch sizes, but in that case you divide by the accumulation steps to correct the magnitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Devin Myers</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>model.eval()
+with torch.no_grad():
+    for images, labels in test_loader:
+        ...</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t># model.eval() REMOVED
+with torch.no_grad():
+    for images, labels in test_loader:
+        ...</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Without model.eval(), the dropout layer is still active during testing, which randomly drops neurons and gives wrong predictions.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>You correctly identified Dropout as the culprit. But consider: our model uses Dropout(p=0.25), which only drops 25% of neurons. Would you expect a dramatic accuracy difference, or a subtle one? Also, Dropout isn't the only layer affected by train vs eval mode — can you think of other layer types that behave differently? And why does PyTorch have this train/eval distinction at all instead of just always using the eval behavior?</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>With Dropout(0.25), only 25% of neurons in the 128-unit FC layer are zeroed during training-mode inference. This means test accuracy will be slightly lower and inconsistent across runs (since the dropout mask is random), but not catastrophically bad — maybe 1-3% lower. The accuracy gap would be larger with higher dropout rates. Beyond Dropout, BatchNorm also behaves differently: in train mode it uses batch statistics, while in eval mode it uses running averages computed during training. Our model doesn't use BatchNorm, so Dropout is the only concern here. The train/eval distinction exists because some techniques (dropout, batch normalization) are regularization methods that help during training but should be disabled at test time to get deterministic, optimal predictions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Vina Dang</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>nn.Linear(128, NUM_CLASSES),
+# No activation after final layer</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>nn.Linear(128, NUM_CLASSES),
+nn.Sigmoid(),  # Added sigmoid to output</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Sigmoid squishes the outputs between 0 and 1 which is wrong because CrossEntropyLoss needs the raw numbers from the linear layer.</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>You're on the right track — CrossEntropyLoss does expect raw logits. But *why* does squashing to [0,1] cause problems? Think about what CrossEntropyLoss does internally: it applies log_softmax. What happens when you apply softmax to values that are already in [0,1] and very close together? How does this affect the gradient magnitude during backpropagation? Also consider: in what scenario *would* sigmoid on the output be appropriate?</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>CrossEntropyLoss internally computes log(softmax(x)). When sigmoid squashes all outputs to [0,1], the values fed to softmax are already compressed into a tiny range. Softmax then produces a nearly uniform distribution (close to 1/10 for each class), making it very hard for the model to express high confidence in any class. The log of these near-uniform probabilities produces gradients that are very small and similar across classes, which slows learning dramatically. The model gets stuck predicting near-random probabilities. Sigmoid on the output would be appropriate for multi-label classification (where multiple classes can be true simultaneously) paired with BCELoss, not for mutually exclusive classification. For single-label classification, raw logits + CrossEntropyLoss is the standard approach because it's numerically stable and produces strong gradients.</t>
         </is>
       </c>
     </row>
